--- a/Bara_Intercropping_Rosemary_Palms_BOQ.xlsx
+++ b/Bara_Intercropping_Rosemary_Palms_BOQ.xlsx
@@ -566,13 +566,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>B8*6.83</f>
+        <f>B8*B5</f>
         <v/>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -720,225 +720,307 @@
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>المحصول المحمل الثانوي</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>روزماري (إكليل الجبل)</t>
-        </is>
+          <t>إنتاجية التمور البرحي للنخلة سنوياً (عند النضج)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>150</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>كجم / نخلة</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>نبات طبي عطري معمر ممتاز للتربة الرملية ومقاوم للجفاف</t>
+          <t>متوسط الإنتاج للنخلة البالغة في ظروف الخدمة الجيدة</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>مسافات زراعة الروزماري</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>1 × 0.5</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>متر</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>1 متر بين الصفوف و 0.5 متر بين النباتات داخل الصف الواحد</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>إجمالي إنتاج التمور للمشروع سنوياً</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>B9*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>كجم / سنة</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي محصول البلح البرحي الجاهز للبيع والتسويق والتصدير</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>عرض حارة زراعة الروزماري</t>
+          <t>معدل إنتاج الفسائل للنخلة سنوياً (العام 4-10)</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>متر</t>
+          <t>فسيلة / نخلة / سنة</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>عرض الحارة الصافية بمنتصف المسافة بين النخيل مع ترك 1.5م حريم خدمة</t>
+          <t>متوسط عدد الفسائل الصالحة للفصل والبيع من كل نخلة سنوياً</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>عدد صفوف الروزماري بالحارة</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>صفوف</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>توزيع الخراطيم والصفوف بالتوازي مع خطوط النخيل</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>إجمالي الفسائل الناتجة للمشروع سنوياً</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>B9*B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>فسيلة / سنة</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي عدد الفسائل المتاحة للبيع كأصول زراعية مستقلة</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>كثافة الروزماري للفدان المحمل</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>5250</v>
+          <t>المحصول المحمل الثانوي</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>روزماري (إكليل الجبل)</t>
+        </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>شتلة / فدان</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>تعادل 62.5% من كثافة الزراعة المنفردة لضمان عدم التظليل</t>
+          <t>نبات طبي عطري معمر ممتاز للتربة الرملية ومقاوم للجفاف</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>إجمالي شتلات الروزماري المطلوبة</t>
-        </is>
-      </c>
-      <c r="B15" s="5">
-        <f>B14*6.83</f>
-        <v/>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>شتلة</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>إجمالي الاحتياج من عقل شتلات الروزماري المجهزة للغرس</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>مسافات زراعة الروزماري</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>1 × 0.5</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>متر</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>1 متر بين الصفوف و 0.5 متر بين النباتات داخل الصف الواحد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>إنتاجية العشب الطازج للفدان سنوياً</t>
+          <t>عرض حارة زراعة الروزماري</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>طن / فدان</t>
+          <t>متر</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>متوسط الإنتاج السنوي للعشب بعد الحصاد على 3-4 حشات</t>
+          <t>عرض الحارة الصافية بمنتصف المسافة بين النخيل مع ترك 1.5م حريم خدمة</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>إجمالي إنتاج العشب للمشروع سنوياً</t>
-        </is>
-      </c>
-      <c r="B17" s="5">
-        <f>B16*6.83</f>
-        <v/>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>طن / سنة</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>إجمالي كميات العشب الطازج الموردة لوحدة التقطير</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>عدد صفوف الروزماري بالحارة</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>صفوف</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>توزيع الخراطيم والصفوف بالتوازي مع خطوط النخيل</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>كثافة الروزماري للفدان المحمل</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>شتلة / فدان</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>تعادل 62.5% من كثافة الزراعة المنفردة لضمان عدم التظليل</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>إجمالي شتلات الروزماري المطلوبة</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>B18*B5</f>
+        <v/>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>شتلة</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي الاحتياج من عقل شتلات الروزماري المجهزة للغرس</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>إنتاجية العشب الطازج للفدان سنوياً</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>طن / فدان</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>متوسط الإنتاج السنوي للعشب بعد الحصاد على 3-4 حشات</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>إجمالي إنتاج العشب للمشروع سنوياً</t>
+        </is>
+      </c>
+      <c r="B21" s="5">
+        <f>B20*B5</f>
+        <v/>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>طن / سنة</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي كميات العشب الطازج الموردة لوحدة التقطير</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>معدل استخلاص الزيت العطري</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B22" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>نسبة استخلاص الزيت من العشب الطازج المجفف جزئياً في الظل</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>إنتاجية زيت الروزماري للفدان سنوياً</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B23" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>كجم / فدان / سنة</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>كمية الزيت العطري النقي المستخلص سنوياً من الفدان الواحد</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>إجمالي إنتاج الزيت العطري للمشروع</t>
         </is>
       </c>
-      <c r="B20" s="5">
-        <f>B19*6.83</f>
-        <v/>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="B24" s="5">
+        <f>B23*B5</f>
+        <v/>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>كجم / سنة</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>إجمالي إنتاج زيت الروزماري النقي الجاهز للبيع والتعبئة والتصدير</t>
         </is>
@@ -960,7 +1042,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1281,8 +1363,9 @@
           <t>فدان</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>6.83</v>
+      <c r="E13" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
       </c>
       <c r="F13" s="11" t="n">
         <v>5000</v>
@@ -1328,7 +1411,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -1386,14 +1469,15 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>شبكة الري بالتنقيط المتكاملة (6.83 فدان)</t>
+          <t>شبكة الري بالتنقيط المتكاملة</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
         <v>28000</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>6.83</v>
+      <c r="D5" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
       </c>
       <c r="E5" s="11">
         <f>'مقايسة شبكة الري'!G14</f>
@@ -1414,8 +1498,9 @@
       <c r="C6" s="11" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>444</v>
+      <c r="D6" s="8">
+        <f>'ملخص المشروع'!B9</f>
+        <v/>
       </c>
       <c r="E6" s="11">
         <f>C6*D6</f>
@@ -1436,8 +1521,9 @@
       <c r="C7" s="11" t="n">
         <v>3.5</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>35850</v>
+      <c r="D7" s="8">
+        <f>'ملخص المشروع'!B19</f>
+        <v/>
       </c>
       <c r="E7" s="11">
         <f>C7*D7</f>
@@ -1480,8 +1566,9 @@
       <c r="C9" s="11" t="n">
         <v>4500</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>6.83</v>
+      <c r="D9" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
       </c>
       <c r="E9" s="11">
         <f>C9*D9</f>
@@ -1549,8 +1636,9 @@
       <c r="B15" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>480</v>
+      <c r="C15" s="8">
+        <f>'ملخص المشروع'!B24</f>
+        <v/>
       </c>
       <c r="D15" s="11">
         <f>B15*C15</f>
@@ -1571,8 +1659,9 @@
       <c r="B16" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="8" t="n">
-        <v>8200</v>
+      <c r="C16" s="8">
+        <f>ROUND('ملخص المشروع'!B21*171.5, 0)</f>
+        <v/>
       </c>
       <c r="D16" s="11">
         <f>B16*C16</f>
@@ -1593,8 +1682,9 @@
       <c r="B17" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="C17" s="8" t="n">
-        <v>66600</v>
+      <c r="C17" s="8">
+        <f>'ملخص المشروع'!B11</f>
+        <v/>
       </c>
       <c r="D17" s="11">
         <f>B17*C17</f>
@@ -1615,8 +1705,9 @@
       <c r="B18" s="11" t="n">
         <v>2000</v>
       </c>
-      <c r="C18" s="8" t="n">
-        <v>666</v>
+      <c r="C18" s="8">
+        <f>'ملخص المشروع'!B13</f>
+        <v/>
       </c>
       <c r="D18" s="11">
         <f>B18*C18</f>

--- a/Bara_Intercropping_Rosemary_Palms_BOQ.xlsx
+++ b/Bara_Intercropping_Rosemary_Palms_BOQ.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,12 +67,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Cairo"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -147,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -197,9 +191,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1410,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1420,109 +1411,93 @@
     <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>التكاليف الاستثمارية (CapEx) والعوائد المتوقعة للمشروع بالكامل</t>
+          <t>التكاليف الاستثمارية (CapEx) والمصاريف التشغيلية (OpEx) والأرباح المتوقعة</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>مزرعة شركة بارا - يشمل تكلفة الفسائل والشتلات وتجهيز وحدة التقطير بالبخار</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>النوع الاستثماري</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>البند المالي</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+          <t>مزرعة شركة بارا - تقييم مالي متكامل يشمل تكاليف الخدمة وتأسيس التربة والمصاريف التشغيلية ومخطط التدفق النقدي</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>أولاً: التكاليف الاستثمارية لتأسيس المشروع وتجهيز التربة (CapEx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>التصنيف المالي</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>البند والبيان الفني</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>سعر الوحدة / الفدان (جنيه)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>الكمية الكلية للمشروع</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>الإجمالي التقديري (جنيه)</t>
         </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>تجهيز الأرض والشبكة</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>شبكة الري بالتنقيط المتكاملة</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>28000</v>
-      </c>
-      <c r="D5" s="8">
-        <f>'ملخص المشروع'!B5</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>'مقايسة شبكة الري'!G14</f>
-        <v/>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>الشتلات والأصول الزراعية</t>
+          <t>شبكة الري والتوزيع</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>فسائل نخيل برحي نسيجي فاخر ومضمون</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="8">
-        <f>'ملخص المشروع'!B9</f>
-        <v/>
+          <t>شبكة الري بالتنقيط المزدوجة المتكاملة</t>
+        </is>
+      </c>
+      <c r="C6" s="11">
+        <f>'مقايسة شبكة الري'!G14</f>
+        <v/>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E6" s="11">
-        <f>C6*D6</f>
+        <f>'مقايسة شبكة الري'!G14</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>الشتلات والأصول الزراعية</t>
+          <t>الأصول الزراعية</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>شتلات وعقل روزماري مجهزة للغرس ومقاومة للأمراض</t>
+          <t>فسائل نخيل برحي نسيجي فاخر ومضمون (65 نخلة/فدان)</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3.5</v>
+        <v>2500</v>
       </c>
       <c r="D7" s="8">
-        <f>'ملخص المشروع'!B19</f>
+        <f>'ملخص المشروع'!B9</f>
         <v/>
       </c>
       <c r="E7" s="11">
@@ -1533,19 +1508,20 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>الأصول الصناعية</t>
+          <t>الأصول الزراعية</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>وحدة تقطير الزيوت العطرية بالبخار سعة 200 لتر استانلس 304</t>
+          <t>شتلات وعقل روزماري مجهزة للغرس ومقاومة للأمراض</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>130000</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
+        <v>3.5</v>
+      </c>
+      <c r="D8" s="8">
+        <f>'ملخص المشروع'!B19</f>
+        <v/>
       </c>
       <c r="E8" s="11">
         <f>C8*D8</f>
@@ -1555,197 +1531,661 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>الخدمات والتشغيل الأساسي</t>
+          <t>الأصول الصناعية</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>أسمدة التأسيس العضوية والجبس الزراعي ومحسنات التربة</t>
+          <t>وحدة تقطير الزيوت العطرية بالبخار سعة 200 لتر استانلس 304</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D9" s="8">
-        <f>'ملخص المشروع'!B5</f>
-        <v/>
+        <v>130000</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E9" s="11">
         <f>C9*D9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>تأسيس وتجهيز التربة</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>حرث حرثاً متعامداً بالميكنة والتسوية الدقيقة بالليزر</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D10" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>تأسيس وتجهيز التربة</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>شق خنادق ري وتوزيع أسمدة وحفر جور النخيل وتكحيل التربة</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D11" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>تأسيس وتجهيز التربة</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>السماد العضوي الأساسي (الكومبوست المكمور النباتي/الحيواني - 15م³/فدان)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D12" s="8">
+        <f>15*'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>تأسيس وتجهيز التربة</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>محسنات التربة الأساسية والجبس الزراعي والسوبر فوسفات والكبريت</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>تأسيس وتجهيز التربة</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>عمالة غرس شتلات الروزماري وفسائل النخيل ومتابعة التثبيت الأولي</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D14" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>C14*D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>إجمالي التكاليف الاستثمارية للمشروع (CapEx)</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="15">
-        <f>SUM(E5:E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>العوائد السنوية المتوقعة للمشروع عند اكتمال النضج (نخيل + روزماري)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>إجمالي التكاليف الاستثمارية لتأسيس وخدمة التربة (CapEx)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="15">
+        <f>SUM(E6:E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>ثانياً: المصروفات التشغيلية السنوية المقدرة للمشروع بالكامل (Annual OpEx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>التصنيف المالي</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>البند والبيان التشغيلي</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>سعر الوحدة للفدان سنوياً (جنيه)</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>المساحة الإجمالية للمشروع</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>التكلفة السنوية الكلية (جنيه)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات تشغيلية</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>مياه ري وطاقة وكهرباء وصيانة طلمبات مائية</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D20" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>C20*D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات تشغيلية</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>برنامج التسميد السنوي والمغذيات والأحماض والعناصر الصغرى</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D21" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
+        <f>C21*D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات تشغيلية</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>برنامج المكافحة والرش الوقائي والمبيدات العضوية المعتمدة</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D22" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>C22*D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات تشغيلية</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>العمالة الدورية وأعمال العزق والتعشيب اليدوي وتقليم النخيل</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D23" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>C23*D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات تشغيلية</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>عمالة الحش والحصاد والتحميل لعشب الروزماري (على مدار السنة)</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D24" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>C24*D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات تشغيلية</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>تكاليف تشغيل المقطرة وعمالة استخلاص الزيوت (وقود وفنيين)</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D25" s="8">
+        <f>'ملخص المشروع'!B5</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>C25*D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>إجمالي المصاريف التشغيلية السنوية للمشروع (OpEx)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="15">
+        <f>SUM(E20:E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>ثالثاً: العوائد والأرباح السنوية المتوقعة للمشروع عند اكتمال النضج (العام الخامس+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>المحصول والمنتج المستخلص</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>متوسط سعر الوحدة (جنيه)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>متوسط سعر بيع الوحدة (جنيه)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>الإنتاج السنوي للمشروع (كجم/لتر/عدد)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>العائد السنوي المتوقع (جنيه)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>توجيهات السوق والتصدير</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>زيت روزماري نقي مستخلص بالبخار</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B31" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C31" s="8">
         <f>'ملخص المشروع'!B24</f>
         <v/>
       </c>
-      <c r="D15" s="11">
-        <f>B15*C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="D31" s="11">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>يباع محلياً لشركات الأدوية والتجميل أو يصدر بأسعار ممتازة</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>هيدروسول الروزماري المقطر (ماء عطري)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B32" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C32" s="8">
         <f>ROUND('ملخص المشروع'!B21*171.5, 0)</f>
         <v/>
       </c>
-      <c r="D16" s="11">
-        <f>B16*C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D32" s="11">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>منتج ثانوي عالي الطلب في صناعات الصابون والشامبو واللوسيونات</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>ثمار البلح البرحي (عند اكتمال النضج)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B33" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C33" s="8">
         <f>'ملخص المشروع'!B11</f>
         <v/>
       </c>
-      <c r="D17" s="11">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="D33" s="11">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>إنتاجية متوسطة 150 كجم للنخلة لعدد 444 نخلة برحي بسعر سوقي متوسط للبيع والتصدير</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>الفسائل الناتجة والمباعة من النخيل نفسه</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B34" s="11" t="n">
         <v>2000</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C34" s="8">
         <f>'ملخص المشروع'!B13</f>
         <v/>
       </c>
-      <c r="D18" s="11">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D34" s="11">
+        <f>B34*C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>متوسط 1.5 فسيلة للنخلة سنوياً لعدد 444 نخلة (مصدر أرباح إضافي هائل ومستمر)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>إجمالي العائد السنوي المتوقع للمشروع بالكامل</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="15">
-        <f>SUM(D15:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>*ملاحظة: عوائد الروزماري تبدأ من العام الثاني، وعوائد النخيل والفسائل تبدأ من العام الرابع وتكتمل عند النضج</t>
-        </is>
+      <c r="C35" s="14" t="inlineStr"/>
+      <c r="D35" s="15">
+        <f>SUM(D31:D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>رابعاً: مخطط التدفقات النقدية السنوية وفترة استرداد رأس المال (5-Year Cash Flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>السنة المالية للمشروع</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>إجمالي الإيرادات السنوية (جنيه)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>التكاليف الرأسمالية (CapEx)</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>المصاريف التشغيلية (OpEx)</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>صافي التدفق النقدي السنوي (جنيه)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>السنة الأولى (التأسيس والزراعة الأولى)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="11">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="D40" s="11">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="E40" s="11">
+        <f>B40-C40-D40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>السنة الثانية (عائد الروزماري الكامل)</t>
+        </is>
+      </c>
+      <c r="B41" s="11">
+        <f>D31+D32</f>
+        <v/>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="11">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="E41" s="11">
+        <f>B41-C41-D41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>السنة الثالثة (أرباح الروزماري المتواصلة)</t>
+        </is>
+      </c>
+      <c r="B42" s="11">
+        <f>D31+D32</f>
+        <v/>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="11">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="E42" s="11">
+        <f>B42-C42-D42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>السنة الرابعة (بشائر البرحي والفسائل)</t>
+        </is>
+      </c>
+      <c r="B43" s="11">
+        <f>(D31+D32)+(0.3*D33)+(0.333*D34)</f>
+        <v/>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="11">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="E43" s="11">
+        <f>B43-C43-D43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>السنة الخامسة ومابعدها (النضج والاستقرار)</t>
+        </is>
+      </c>
+      <c r="B44" s="11">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="11">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="E44" s="11">
+        <f>B44-C44-D44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>صافي التدفق النقدي التراكمي (نهاية السنة الخامسة)</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="14" t="inlineStr"/>
+      <c r="E45" s="15">
+        <f>SUM(E40:E44)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
